--- a/Excel/excel.xlsx
+++ b/Excel/excel.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Student Details" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Updated Student Details" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -122,6 +123,16 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Employee_Table" displayName="Employee_Table" ref="A1:C25" headerRowCount="1">
+  <autoFilter ref="A1:A1"/>
+  <tableColumns count="1">
+    <tableColumn id="1" name="None"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,9 +424,601 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Dept</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sethu</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>cse</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sethumadavan</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sethu raman</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bio</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sethu raja</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sethu Kumar</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sethu Raj</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ECE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sethu</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cse</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sethumadavan</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sethu raman</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bio</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sethu raja</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sethu Kumar</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sethu Raj</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ECE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sethu</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cse</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sethumadavan</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sethu raman</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bio</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sethu raja</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sethu Kumar</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sethu Raj</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ECE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sethu</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>cse</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sethumadavan</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sethu raman</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bio</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sethu raja</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sethu Kumar</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sethu Raj</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ECE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Dept</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sethu</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>cse</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sethumadavan</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sethu raman</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bio</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sethu raja</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sethu Kumar</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sethu Raj</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ECE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sethu</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cse</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sethumadavan</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sethu raman</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bio</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sethu raja</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mech</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sethu Kumar</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sethu Raj</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ECE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Excel/excel.xlsx
+++ b/Excel/excel.xlsx
@@ -122,6 +122,21 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Prawin</author>
+  </authors>
+  <commentList>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>This is a comment</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +477,9 @@
           <t>Comments</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="F2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -470,6 +488,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
